--- a/xls/square_20_tri3_15.xlsx
+++ b/xls/square_20_tri3_15.xlsx
@@ -456,6 +456,76 @@
         <v>10</v>
       </c>
     </row>
+    <row r="13" spans="1:11">
+      <c r="A13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13">
+        <v>256</v>
+      </c>
+      <c r="C13" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13">
+        <v>441</v>
+      </c>
+      <c r="E13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13">
+        <v>196</v>
+      </c>
+      <c r="G13" t="s">
+        <v>13</v>
+      </c>
+      <c r="H13">
+        <v>1014</v>
+      </c>
+      <c r="I13">
+        <v>3.828643956453668</v>
+      </c>
+      <c r="J13">
+        <v>0.32036298050356815</v>
+      </c>
+      <c r="K13">
+        <v>1.2079480990041265</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14">
+        <v>256</v>
+      </c>
+      <c r="C14" t="s">
+        <v>11</v>
+      </c>
+      <c r="D14">
+        <v>441</v>
+      </c>
+      <c r="E14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14">
+        <v>225</v>
+      </c>
+      <c r="G14" t="s">
+        <v>13</v>
+      </c>
+      <c r="H14">
+        <v>1176</v>
+      </c>
+      <c r="I14">
+        <v>2.778867070333268</v>
+      </c>
+      <c r="J14">
+        <v>-0.4317409790299322</v>
+      </c>
+      <c r="K14">
+        <v>0.651779326915909</v>
+      </c>
+    </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
         <v>11</v>
